--- a/1-LATEX/2-DADOS/3-OUTPUT/subgrupos.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/subgrupos.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -736,19 +736,19 @@
         <v>4</v>
       </c>
       <c r="E11">
-        <v>0.2438415186127764</v>
+        <v>0.2445853376472027</v>
       </c>
       <c r="F11">
-        <v>0.04053559281720272</v>
+        <v>0.02530659356483455</v>
       </c>
       <c r="G11">
-        <v>0.1148391710191848</v>
+        <v>0.184744752778593</v>
       </c>
       <c r="H11">
-        <v>0.3728438662063681</v>
+        <v>0.3044259225158124</v>
       </c>
       <c r="I11">
-        <v>8.536195633921965E-09</v>
+        <v>5.152563934429814E-08</v>
       </c>
     </row>
     <row r="12">
@@ -771,19 +771,19 @@
         <v>10</v>
       </c>
       <c r="E12">
-        <v>0.06035643347296015</v>
+        <v>0.07536796405836071</v>
       </c>
       <c r="F12">
-        <v>0.08335138227464292</v>
+        <v>0.06455280857870195</v>
       </c>
       <c r="G12">
-        <v>-0.1281974929687547</v>
+        <v>-0.05974261707647754</v>
       </c>
       <c r="H12">
-        <v>0.248910359914675</v>
+        <v>0.210478545193199</v>
       </c>
       <c r="I12">
-        <v>3.634690257096481</v>
+        <v>2.626311304879172</v>
       </c>
     </row>
     <row r="13">
@@ -806,19 +806,19 @@
         <v>3</v>
       </c>
       <c r="E13">
-        <v>0.2700799003446532</v>
+        <v>0.214255226730735</v>
       </c>
       <c r="F13">
-        <v>0.08961206559946612</v>
+        <v>0.1553644230009015</v>
       </c>
       <c r="G13">
-        <v>-0.1154896983253777</v>
+        <v>-0.1851217369394992</v>
       </c>
       <c r="H13">
-        <v>0.6556494990146842</v>
+        <v>0.6136321904009692</v>
       </c>
       <c r="I13">
-        <v>1.594932008395434E-08</v>
+        <v>5.01196456629249</v>
       </c>
     </row>
     <row r="14">
@@ -841,19 +841,19 @@
         <v>12</v>
       </c>
       <c r="E14">
-        <v>0.1229308080283124</v>
+        <v>0.0483859328802883</v>
       </c>
       <c r="F14">
-        <v>0.1000778603649634</v>
+        <v>0.1053313397763866</v>
       </c>
       <c r="G14">
-        <v>-0.09733907748869527</v>
+        <v>-0.1695085447637684</v>
       </c>
       <c r="H14">
-        <v>0.34320069354532</v>
+        <v>0.266280410524345</v>
       </c>
       <c r="I14">
-        <v>1.772539521693059</v>
+        <v>3.257429710875688</v>
       </c>
     </row>
     <row r="15">
@@ -876,19 +876,19 @@
         <v>4</v>
       </c>
       <c r="E15">
-        <v>0.2273051208735526</v>
+        <v>-0.2605025592194234</v>
       </c>
       <c r="F15">
-        <v>0.5667092671026301</v>
+        <v>0.3759866995422155</v>
       </c>
       <c r="G15">
-        <v>-1.576216692387251</v>
+        <v>-1.149569827233276</v>
       </c>
       <c r="H15">
-        <v>2.030826934134357</v>
+        <v>0.6285647087944291</v>
       </c>
       <c r="I15">
-        <v>1.642588412644197E-08</v>
+        <v>1.864843340628868E-08</v>
       </c>
     </row>
     <row r="16">
@@ -911,19 +911,19 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <v>-0.05161019914874498</v>
+        <v>-0.1035467502246228</v>
       </c>
       <c r="F16">
-        <v>0.09661940896332916</v>
+        <v>0.08377835794555406</v>
       </c>
       <c r="G16">
-        <v>-0.2999782967997954</v>
+        <v>-0.2879416727996327</v>
       </c>
       <c r="H16">
-        <v>0.1967578985023055</v>
+        <v>0.0808481723503871</v>
       </c>
       <c r="I16">
-        <v>1.081138702534743E-09</v>
+        <v>1.16656676226991</v>
       </c>
     </row>
     <row r="17">
@@ -946,19 +946,19 @@
         <v>12</v>
       </c>
       <c r="E17">
-        <v>-0.001694152876888544</v>
+        <v>-0.0215560906523817</v>
       </c>
       <c r="F17">
-        <v>0.05934184411977059</v>
+        <v>0.04750458018209358</v>
       </c>
       <c r="G17">
-        <v>-0.1323046711569749</v>
+        <v>-0.1198268019758315</v>
       </c>
       <c r="H17">
-        <v>0.1289163654031978</v>
+        <v>0.0767146206710681</v>
       </c>
       <c r="I17">
-        <v>1.867646335734729</v>
+        <v>1.698653618600558</v>
       </c>
     </row>
     <row r="18">
@@ -981,19 +981,19 @@
         <v>16</v>
       </c>
       <c r="E18">
-        <v>0.01727212689462171</v>
+        <v>-0.1616160172438303</v>
       </c>
       <c r="F18">
-        <v>0.14446213490614</v>
+        <v>0.1514636145667093</v>
       </c>
       <c r="G18">
-        <v>-0.2906416249016653</v>
+        <v>-0.4705280957924368</v>
       </c>
       <c r="H18">
-        <v>0.3251858786909087</v>
+        <v>0.1472960613047763</v>
       </c>
       <c r="I18">
-        <v>6.316939737703049</v>
+        <v>14.52780776275285</v>
       </c>
     </row>
     <row r="19">
@@ -1016,19 +1016,19 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-0.07355139460699693</v>
+        <v>-0.1918371612398533</v>
       </c>
       <c r="F19">
-        <v>0.1360919892746167</v>
+        <v>0.08095214968695316</v>
       </c>
       <c r="G19">
-        <v>-0.4065564960089506</v>
+        <v>-0.3667236480968311</v>
       </c>
       <c r="H19">
-        <v>0.2594537067949567</v>
+        <v>-0.0169506743828754</v>
       </c>
       <c r="I19">
-        <v>1.234461646070667E-08</v>
+        <v>4.706842134633484E-09</v>
       </c>
     </row>
     <row r="20">
@@ -1051,19 +1051,19 @@
         <v>4</v>
       </c>
       <c r="E20">
-        <v>-0.05038479591992623</v>
+        <v>0.01852167271213953</v>
       </c>
       <c r="F20">
-        <v>0.3838610795855891</v>
+        <v>0.4471594074010083</v>
       </c>
       <c r="G20">
-        <v>-1.2720020703893</v>
+        <v>-1.404539131244052</v>
       </c>
       <c r="H20">
-        <v>1.171232478549448</v>
+        <v>1.441582476668331</v>
       </c>
       <c r="I20">
-        <v>1.841480580630848E-08</v>
+        <v>1.384722476922143E-08</v>
       </c>
     </row>
     <row r="21">
@@ -1086,19 +1086,19 @@
         <v>10</v>
       </c>
       <c r="E21">
-        <v>0.2308163782029877</v>
+        <v>-0.0639217119377202</v>
       </c>
       <c r="F21">
-        <v>0.0388667764866695</v>
+        <v>0.2075597141160282</v>
       </c>
       <c r="G21">
-        <v>0.1428936213787915</v>
+        <v>-0.533454405933641</v>
       </c>
       <c r="H21">
-        <v>0.318739135027184</v>
+        <v>0.4056109820582006</v>
       </c>
       <c r="I21">
-        <v>9.049987963422489E-08</v>
+        <v>17.6732291563625</v>
       </c>
     </row>
     <row r="22">
@@ -1121,19 +1121,19 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>0.3002107575754079</v>
+        <v>0.6422929817855093</v>
       </c>
       <c r="F22">
-        <v>0.4158142105787668</v>
+        <v>0.2112326638264767</v>
       </c>
       <c r="G22">
-        <v>-1.488893390639941</v>
+        <v>-0.2665678158397314</v>
       </c>
       <c r="H22">
-        <v>2.089314905790757</v>
+        <v>1.55115377941075</v>
       </c>
       <c r="I22">
-        <v>48.41913541890619</v>
+        <v>1.774907573897924E-08</v>
       </c>
     </row>
     <row r="23">
@@ -1156,19 +1156,19 @@
         <v>12</v>
       </c>
       <c r="E23">
-        <v>-0.09397216519073945</v>
+        <v>-0.06649650192953685</v>
       </c>
       <c r="F23">
-        <v>0.1666394570408505</v>
+        <v>0.1544443670309595</v>
       </c>
       <c r="G23">
-        <v>-0.4607431372233796</v>
+        <v>-0.406426261824425</v>
       </c>
       <c r="H23">
-        <v>0.2727988068419007</v>
+        <v>0.2734332579653512</v>
       </c>
       <c r="I23">
-        <v>1.000784207775424E-08</v>
+        <v>8.592356100364199E-09</v>
       </c>
     </row>
     <row r="24">
@@ -1191,19 +1191,19 @@
         <v>4</v>
       </c>
       <c r="E24">
-        <v>-0.171350183295798</v>
+        <v>-0.02930836042933228</v>
       </c>
       <c r="F24">
-        <v>0.3841623167066624</v>
+        <v>0.5082694128916621</v>
       </c>
       <c r="G24">
-        <v>-1.393926128728146</v>
+        <v>-1.646848475575122</v>
       </c>
       <c r="H24">
-        <v>1.05122576213655</v>
+        <v>1.588231754716458</v>
       </c>
       <c r="I24">
-        <v>1.577912322242672E-08</v>
+        <v>1.008693311007063E-08</v>
       </c>
     </row>
     <row r="25">
@@ -1226,19 +1226,19 @@
         <v>6</v>
       </c>
       <c r="E25">
-        <v>-0.230513740819908</v>
+        <v>-0.06721034877494055</v>
       </c>
       <c r="F25">
-        <v>0.1662075370288635</v>
+        <v>0.3400445178869844</v>
       </c>
       <c r="G25">
-        <v>-0.6577638164521546</v>
+        <v>-0.9413226097629305</v>
       </c>
       <c r="H25">
-        <v>0.1967363348123386</v>
+        <v>0.8069019122130493</v>
       </c>
       <c r="I25">
-        <v>0.4730199396105959</v>
+        <v>1.233412932761798E-08</v>
       </c>
     </row>
     <row r="26">
@@ -1261,19 +1261,19 @@
         <v>12</v>
       </c>
       <c r="E26">
-        <v>0.1315928818416824</v>
+        <v>0.03903534494302381</v>
       </c>
       <c r="F26">
-        <v>0.07762920776026538</v>
+        <v>0.1323501484152196</v>
       </c>
       <c r="G26">
-        <v>-0.03926785242833236</v>
+        <v>-0.2522653676548005</v>
       </c>
       <c r="H26">
-        <v>0.3024536161116972</v>
+        <v>0.330336057540848</v>
       </c>
       <c r="I26">
-        <v>7.555189968973764E-09</v>
+        <v>7.976932219989193</v>
       </c>
     </row>
     <row r="27">
@@ -1296,19 +1296,19 @@
         <v>16</v>
       </c>
       <c r="E27">
-        <v>0.1222474205725065</v>
+        <v>-0.02630155695842439</v>
       </c>
       <c r="F27">
-        <v>0.1374748560976752</v>
+        <v>0.1913597648346051</v>
       </c>
       <c r="G27">
-        <v>-0.1707732989827789</v>
+        <v>-0.434175240753569</v>
       </c>
       <c r="H27">
-        <v>0.4152681401277918</v>
+        <v>0.3815721268367202</v>
       </c>
       <c r="I27">
-        <v>9.641246690311023</v>
+        <v>11.01203953608417</v>
       </c>
     </row>
     <row r="28">
@@ -1331,19 +1331,19 @@
         <v>7</v>
       </c>
       <c r="E28">
-        <v>-0.3581059318736136</v>
+        <v>-0.1442838711524659</v>
       </c>
       <c r="F28">
-        <v>0.1981623054265396</v>
+        <v>0.3190792740291604</v>
       </c>
       <c r="G28">
-        <v>-0.8429916254720223</v>
+        <v>-0.9250427282291518</v>
       </c>
       <c r="H28">
-        <v>0.1267797617247952</v>
+        <v>0.6364749859242198</v>
       </c>
       <c r="I28">
-        <v>1.150376951434819E-08</v>
+        <v>9.254343456888847E-09</v>
       </c>
     </row>
     <row r="29">
@@ -1366,19 +1366,19 @@
         <v>4</v>
       </c>
       <c r="E29">
-        <v>0.01852167271213953</v>
+        <v>-0.4391797361688963</v>
       </c>
       <c r="F29">
-        <v>0.4471594074010083</v>
+        <v>0.2498146577473095</v>
       </c>
       <c r="G29">
-        <v>-1.404539131244052</v>
+        <v>-1.234201470722536</v>
       </c>
       <c r="H29">
-        <v>1.441582476668331</v>
+        <v>0.3558419983847431</v>
       </c>
       <c r="I29">
-        <v>1.384722476922143E-08</v>
+        <v>1.282087779903722E-08</v>
       </c>
     </row>
     <row r="30">
@@ -1401,19 +1401,19 @@
         <v>10</v>
       </c>
       <c r="E30">
-        <v>-0.0639217119377202</v>
+        <v>-0.06115621414169668</v>
       </c>
       <c r="F30">
-        <v>0.2075597141160282</v>
+        <v>0.2360925795471624</v>
       </c>
       <c r="G30">
-        <v>-0.533454405933641</v>
+        <v>-0.5952347340478151</v>
       </c>
       <c r="H30">
-        <v>0.4056109820582006</v>
+        <v>0.4729223057644217</v>
       </c>
       <c r="I30">
-        <v>17.6732291563625</v>
+        <v>30.52408469398196</v>
       </c>
     </row>
     <row r="31">
@@ -1436,19 +1436,19 @@
         <v>3</v>
       </c>
       <c r="E31">
-        <v>0.6422929817855093</v>
+        <v>-0.6815385465663448</v>
       </c>
       <c r="F31">
-        <v>0.2112326638264767</v>
+        <v>0.3592992131225712</v>
       </c>
       <c r="G31">
-        <v>-0.2665678158397314</v>
+        <v>-2.22747828670501</v>
       </c>
       <c r="H31">
-        <v>1.55115377941075</v>
+        <v>0.8644011935723204</v>
       </c>
       <c r="I31">
-        <v>1.774907573897924E-08</v>
+        <v>28.11527516229442</v>
       </c>
     </row>
     <row r="32">
@@ -1471,19 +1471,19 @@
         <v>12</v>
       </c>
       <c r="E32">
-        <v>-0.06649650192953685</v>
+        <v>-0.4643969897354381</v>
       </c>
       <c r="F32">
-        <v>0.1544443670309595</v>
+        <v>0.1390306437835358</v>
       </c>
       <c r="G32">
-        <v>-0.406426261824425</v>
+        <v>-0.7704013735009873</v>
       </c>
       <c r="H32">
-        <v>0.2734332579653512</v>
+        <v>-0.1583926059698889</v>
       </c>
       <c r="I32">
-        <v>8.592356100364199E-09</v>
+        <v>1.436139404283941E-07</v>
       </c>
     </row>
     <row r="33">
@@ -1506,19 +1506,19 @@
         <v>4</v>
       </c>
       <c r="E33">
-        <v>-0.02930836042933228</v>
+        <v>-0.5568514863916642</v>
       </c>
       <c r="F33">
-        <v>0.5082694128916621</v>
+        <v>0.1514890851747054</v>
       </c>
       <c r="G33">
-        <v>-1.646848475575122</v>
+        <v>-1.038957365796714</v>
       </c>
       <c r="H33">
-        <v>1.588231754716458</v>
+        <v>-0.07474560698661387</v>
       </c>
       <c r="I33">
-        <v>1.008693311007063E-08</v>
+        <v>2.366592936479407E-09</v>
       </c>
     </row>
     <row r="34">
@@ -1541,19 +1541,19 @@
         <v>6</v>
       </c>
       <c r="E34">
-        <v>-0.06721034877494055</v>
+        <v>-0.1252995893237017</v>
       </c>
       <c r="F34">
-        <v>0.3400445178869844</v>
+        <v>0.3343568956024552</v>
       </c>
       <c r="G34">
-        <v>-0.9413226097629305</v>
+        <v>-0.9847913517791207</v>
       </c>
       <c r="H34">
-        <v>0.8069019122130493</v>
+        <v>0.7341921731317174</v>
       </c>
       <c r="I34">
-        <v>1.233412932761798E-08</v>
+        <v>56.54514021118624</v>
       </c>
     </row>
     <row r="35">
@@ -1576,19 +1576,19 @@
         <v>12</v>
       </c>
       <c r="E35">
-        <v>0.03903534494302381</v>
+        <v>-0.3952600741792041</v>
       </c>
       <c r="F35">
-        <v>0.1323501484152196</v>
+        <v>0.1536207885864818</v>
       </c>
       <c r="G35">
-        <v>-0.2522653676548005</v>
+        <v>-0.7333771501396253</v>
       </c>
       <c r="H35">
-        <v>0.330336057540848</v>
+        <v>-0.05714299821878271</v>
       </c>
       <c r="I35">
-        <v>7.976932219989193</v>
+        <v>28.60635932672484</v>
       </c>
     </row>
     <row r="36">
@@ -1611,19 +1611,19 @@
         <v>16</v>
       </c>
       <c r="E36">
-        <v>-0.02630155695842439</v>
+        <v>-0.2413144205325608</v>
       </c>
       <c r="F36">
-        <v>0.1913597648346051</v>
+        <v>0.1695520435152585</v>
       </c>
       <c r="G36">
-        <v>-0.434175240753569</v>
+        <v>-0.6027060466318898</v>
       </c>
       <c r="H36">
-        <v>0.3815721268367202</v>
+        <v>0.1200772055667681</v>
       </c>
       <c r="I36">
-        <v>11.01203953608417</v>
+        <v>37.73451746931129</v>
       </c>
     </row>
     <row r="37">
@@ -1646,19 +1646,19 @@
         <v>7</v>
       </c>
       <c r="E37">
-        <v>-0.1442838711524659</v>
+        <v>-0.1562821132726427</v>
       </c>
       <c r="F37">
-        <v>0.3190792740291604</v>
+        <v>0.2962381923971254</v>
       </c>
       <c r="G37">
-        <v>-0.9250427282291518</v>
+        <v>-0.8811508570109324</v>
       </c>
       <c r="H37">
-        <v>0.6364749859242198</v>
+        <v>0.5685866304656472</v>
       </c>
       <c r="I37">
-        <v>9.254343456888847E-09</v>
+        <v>29.86848240885717</v>
       </c>
     </row>
     <row r="38">
@@ -1681,19 +1681,19 @@
         <v>4</v>
       </c>
       <c r="E38">
-        <v>-0.4391797361688963</v>
+        <v>0.182322</v>
       </c>
       <c r="F38">
-        <v>0.2498146577473095</v>
+        <v>0.4651057331307167</v>
       </c>
       <c r="G38">
-        <v>-1.234201470722536</v>
+        <v>-1.29785202196812</v>
       </c>
       <c r="H38">
-        <v>0.3558419983847431</v>
+        <v>1.66249602196812</v>
       </c>
       <c r="I38">
-        <v>1.282087779903722E-08</v>
+        <v>1.199541600270954E-08</v>
       </c>
     </row>
     <row r="39">
@@ -1716,19 +1716,19 @@
         <v>10</v>
       </c>
       <c r="E39">
-        <v>-0.06115621414169668</v>
+        <v>0.1021792714368827</v>
       </c>
       <c r="F39">
-        <v>0.2360925795471624</v>
+        <v>0.1409308824708284</v>
       </c>
       <c r="G39">
-        <v>-0.5952347340478151</v>
+        <v>-0.2166285338039739</v>
       </c>
       <c r="H39">
-        <v>0.4729223057644217</v>
+        <v>0.4209870766777392</v>
       </c>
       <c r="I39">
-        <v>30.52408469398196</v>
+        <v>9.881778784723961</v>
       </c>
     </row>
     <row r="40">
@@ -1751,19 +1751,19 @@
         <v>3</v>
       </c>
       <c r="E40">
-        <v>-0.6815385465663448</v>
+        <v>0.3823341142177097</v>
       </c>
       <c r="F40">
-        <v>0.3592992131225712</v>
+        <v>0.2893834533086359</v>
       </c>
       <c r="G40">
-        <v>-2.22747828670501</v>
+        <v>-0.8627823911050188</v>
       </c>
       <c r="H40">
-        <v>0.8644011935723204</v>
+        <v>1.627450619540438</v>
       </c>
       <c r="I40">
-        <v>28.11527516229442</v>
+        <v>9.210202013089315</v>
       </c>
     </row>
     <row r="41">
@@ -1786,19 +1786,19 @@
         <v>12</v>
       </c>
       <c r="E41">
-        <v>-0.4643969897354381</v>
+        <v>-0.2258594081650757</v>
       </c>
       <c r="F41">
-        <v>0.1390306437835358</v>
+        <v>0.1504951444705828</v>
       </c>
       <c r="G41">
-        <v>-0.7704013735009873</v>
+        <v>-0.5570969878106757</v>
       </c>
       <c r="H41">
-        <v>-0.1583926059698889</v>
+        <v>0.1053781714805243</v>
       </c>
       <c r="I41">
-        <v>1.436139404283941E-07</v>
+        <v>1.910784240236076E-08</v>
       </c>
     </row>
     <row r="42">
@@ -1821,19 +1821,19 @@
         <v>4</v>
       </c>
       <c r="E42">
-        <v>-0.5568514863916642</v>
+        <v>0.2273051208735526</v>
       </c>
       <c r="F42">
-        <v>0.1514890851747054</v>
+        <v>0.5667092671026301</v>
       </c>
       <c r="G42">
-        <v>-1.038957365796714</v>
+        <v>-1.576216692387251</v>
       </c>
       <c r="H42">
-        <v>-0.07474560698661387</v>
+        <v>2.030826934134357</v>
       </c>
       <c r="I42">
-        <v>2.366592936479407E-09</v>
+        <v>1.642588412644197E-08</v>
       </c>
     </row>
     <row r="43">
@@ -1856,19 +1856,19 @@
         <v>6</v>
       </c>
       <c r="E43">
-        <v>-0.1252995893237017</v>
+        <v>0.5095467140488308</v>
       </c>
       <c r="F43">
-        <v>0.3343568956024552</v>
+        <v>0.4569466603017722</v>
       </c>
       <c r="G43">
-        <v>-0.9847913517791207</v>
+        <v>-0.6650720707775821</v>
       </c>
       <c r="H43">
-        <v>0.7341921731317174</v>
+        <v>1.684165498875244</v>
       </c>
       <c r="I43">
-        <v>56.54514021118624</v>
+        <v>19.00046182544477</v>
       </c>
     </row>
     <row r="44">
@@ -1891,19 +1891,19 @@
         <v>12</v>
       </c>
       <c r="E44">
-        <v>-0.3952600741792041</v>
+        <v>0.03860338871764885</v>
       </c>
       <c r="F44">
-        <v>0.1536207885864818</v>
+        <v>0.139866571421634</v>
       </c>
       <c r="G44">
-        <v>-0.7333771501396253</v>
+        <v>-0.2692408593742649</v>
       </c>
       <c r="H44">
-        <v>-0.05714299821878271</v>
+        <v>0.3464476368095626</v>
       </c>
       <c r="I44">
-        <v>28.60635932672484</v>
+        <v>10.00000780070796</v>
       </c>
     </row>
     <row r="45">
@@ -1926,19 +1926,19 @@
         <v>16</v>
       </c>
       <c r="E45">
-        <v>-0.2413144205325608</v>
+        <v>0.2054331076203366</v>
       </c>
       <c r="F45">
-        <v>0.1695520435152585</v>
+        <v>0.1311936714566219</v>
       </c>
       <c r="G45">
-        <v>-0.6027060466318898</v>
+        <v>-0.07419958378619862</v>
       </c>
       <c r="H45">
-        <v>0.1200772055667681</v>
+        <v>0.4850657990268719</v>
       </c>
       <c r="I45">
-        <v>37.73451746931129</v>
+        <v>2.891479016641617</v>
       </c>
     </row>
     <row r="46">
@@ -1961,19 +1961,19 @@
         <v>7</v>
       </c>
       <c r="E46">
-        <v>-0.1562821132726427</v>
+        <v>0.6879586842724434</v>
       </c>
       <c r="F46">
-        <v>0.2962381923971254</v>
+        <v>0.3867899354060747</v>
       </c>
       <c r="G46">
-        <v>-0.8811508570109324</v>
+        <v>-0.258482192576278</v>
       </c>
       <c r="H46">
-        <v>0.5685866304656472</v>
+        <v>1.634399561121165</v>
       </c>
       <c r="I46">
-        <v>29.86848240885717</v>
+        <v>13.24057488958442</v>
       </c>
     </row>
     <row r="47">
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>0.182322</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>0.4651057331307167</v>
+        <v>1.110720757145547</v>
       </c>
       <c r="G47">
-        <v>-1.29785202196812</v>
+        <v>-3.083855209418343</v>
       </c>
       <c r="H47">
-        <v>1.66249602196812</v>
+        <v>3.083855209418343</v>
       </c>
       <c r="I47">
-        <v>1.199541600270954E-08</v>
+        <v>2.869237346927056E-08</v>
       </c>
     </row>
     <row r="48">
@@ -2028,22 +2028,22 @@
         </is>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E48">
-        <v>0.1021792714368827</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>0.1409308824708284</v>
+        <v>0.7488477817353316</v>
       </c>
       <c r="G48">
-        <v>-0.2166285338039739</v>
+        <v>-1.66853683670823</v>
       </c>
       <c r="H48">
-        <v>0.4209870766777392</v>
+        <v>1.66853683670823</v>
       </c>
       <c r="I48">
-        <v>9.881778784723961</v>
+        <v>3.743529903292116E-08</v>
       </c>
     </row>
     <row r="49">
@@ -2063,22 +2063,22 @@
         </is>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>0.3823341142177097</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>0.2893834533086359</v>
+        <v>1.241823558557728</v>
       </c>
       <c r="G49">
-        <v>-0.8627823911050188</v>
+        <v>-3.952036795746309</v>
       </c>
       <c r="H49">
-        <v>1.627450619540438</v>
+        <v>3.952036795746309</v>
       </c>
       <c r="I49">
-        <v>9.210202013089315</v>
+        <v>3.819266496611709E-08</v>
       </c>
     </row>
     <row r="50">
@@ -2098,22 +2098,22 @@
         </is>
       </c>
       <c r="D50">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E50">
-        <v>-0.2258594081650757</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>0.1504951444705828</v>
+        <v>0.6023729059485836</v>
       </c>
       <c r="G50">
-        <v>-0.5570969878106757</v>
+        <v>-1.276973515427709</v>
       </c>
       <c r="H50">
-        <v>0.1053781714805243</v>
+        <v>1.276973515427709</v>
       </c>
       <c r="I50">
-        <v>1.910784240236076E-08</v>
+        <v>4.792086731460409E-08</v>
       </c>
     </row>
     <row r="51">
@@ -2133,22 +2133,22 @@
         </is>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E51">
-        <v>0.2273051208735526</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>0.5667092671026301</v>
+        <v>1.110720757145547</v>
       </c>
       <c r="G51">
-        <v>-1.576216692387251</v>
+        <v>-3.083855209418343</v>
       </c>
       <c r="H51">
-        <v>2.030826934134357</v>
+        <v>3.083855209418343</v>
       </c>
       <c r="I51">
-        <v>1.642588412644197E-08</v>
+        <v>2.869237346927056E-08</v>
       </c>
     </row>
     <row r="52">
@@ -2168,22 +2168,22 @@
         </is>
       </c>
       <c r="D52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E52">
-        <v>0.5095467140488308</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>0.4569466603017722</v>
+        <v>0.9387303737320342</v>
       </c>
       <c r="G52">
-        <v>-0.6650720707775821</v>
+        <v>-2.296990476514661</v>
       </c>
       <c r="H52">
-        <v>1.684165498875244</v>
+        <v>2.296990476514661</v>
       </c>
       <c r="I52">
-        <v>19.00046182544477</v>
+        <v>3.192985951359382E-08</v>
       </c>
     </row>
     <row r="53">
@@ -2203,22 +2203,22 @@
         </is>
       </c>
       <c r="D53">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E53">
-        <v>0.03860338871764885</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>0.139866571421634</v>
+        <v>0.6637826129601136</v>
       </c>
       <c r="G53">
-        <v>-0.2692408593742649</v>
+        <v>-1.434015151744002</v>
       </c>
       <c r="H53">
-        <v>0.3464476368095626</v>
+        <v>1.434015151744002</v>
       </c>
       <c r="I53">
-        <v>10.00000780070796</v>
+        <v>2.843778947481258E-08</v>
       </c>
     </row>
     <row r="54">
@@ -2238,22 +2238,22 @@
         </is>
       </c>
       <c r="D54">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E54">
-        <v>0.2054331076203366</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>0.1311936714566219</v>
+        <v>0.5854012395427431</v>
       </c>
       <c r="G54">
-        <v>-0.07419958378619862</v>
+        <v>-1.235088654470212</v>
       </c>
       <c r="H54">
-        <v>0.4850657990268719</v>
+        <v>1.235088654470212</v>
       </c>
       <c r="I54">
-        <v>2.891479016641617</v>
+        <v>4.291544873132511E-08</v>
       </c>
     </row>
     <row r="55">
@@ -2273,22 +2273,652 @@
         </is>
       </c>
       <c r="D55">
+        <v>10</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0.7853981794336395</v>
+      </c>
+      <c r="G55">
+        <v>-1.776694117254477</v>
+      </c>
+      <c r="H55">
+        <v>1.776694117254477</v>
+      </c>
+      <c r="I55">
+        <v>4.177273346931159E-08</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tipo_Intervencao</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ethnobotanical survey</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>1.110720757145547</v>
+      </c>
+      <c r="G56">
+        <v>-3.083855209418343</v>
+      </c>
+      <c r="H56">
+        <v>3.083855209418343</v>
+      </c>
+      <c r="I56">
+        <v>2.869237346927056E-08</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Regiao</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>11</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0.7488477817353316</v>
+      </c>
+      <c r="G57">
+        <v>-1.66853683670823</v>
+      </c>
+      <c r="H57">
+        <v>1.66853683670823</v>
+      </c>
+      <c r="I57">
+        <v>3.743529903292116E-08</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Regiao</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>America Central</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>1.241823558557728</v>
+      </c>
+      <c r="G58">
+        <v>-3.952036795746309</v>
+      </c>
+      <c r="H58">
+        <v>3.952036795746309</v>
+      </c>
+      <c r="I58">
+        <v>3.819266496611709E-08</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Regiao</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>America do Sul</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>17</v>
+      </c>
+      <c r="E59">
+        <v>0.09705520365518107</v>
+      </c>
+      <c r="F59">
+        <v>0.4290625201688064</v>
+      </c>
+      <c r="G59">
+        <v>-0.8125167065478983</v>
+      </c>
+      <c r="H59">
+        <v>1.006627113858261</v>
+      </c>
+      <c r="I59">
+        <v>2.378845066632883E-08</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Regiao</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>1.110720757145547</v>
+      </c>
+      <c r="G60">
+        <v>-3.083855209418343</v>
+      </c>
+      <c r="H60">
+        <v>3.083855209418343</v>
+      </c>
+      <c r="I60">
+        <v>2.869237346927056E-08</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Regiao</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D61">
         <v>7</v>
       </c>
-      <c r="E55">
-        <v>0.6879586842724434</v>
-      </c>
-      <c r="F55">
-        <v>0.3867899354060747</v>
-      </c>
-      <c r="G55">
-        <v>-0.258482192576278</v>
-      </c>
-      <c r="H55">
-        <v>1.634399561121165</v>
-      </c>
-      <c r="I55">
-        <v>13.24057488958442</v>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0.9387303737320342</v>
+      </c>
+      <c r="G61">
+        <v>-2.296990476514661</v>
+      </c>
+      <c r="H61">
+        <v>2.296990476514661</v>
+      </c>
+      <c r="I61">
+        <v>3.192985951359382E-08</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tipo_Comunidade</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Agricultores</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>14</v>
+      </c>
+      <c r="E62">
+        <v>0.07198369525816804</v>
+      </c>
+      <c r="F62">
+        <v>0.5225685070681866</v>
+      </c>
+      <c r="G62">
+        <v>-1.056956928266497</v>
+      </c>
+      <c r="H62">
+        <v>1.200924318782833</v>
+      </c>
+      <c r="I62">
+        <v>2.097143184476203E-08</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tipo_Comunidade</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Indigena</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>18</v>
+      </c>
+      <c r="E63">
+        <v>0.0627362812181413</v>
+      </c>
+      <c r="F63">
+        <v>0.4878491476156913</v>
+      </c>
+      <c r="G63">
+        <v>-0.9665354500541492</v>
+      </c>
+      <c r="H63">
+        <v>1.092008012490432</v>
+      </c>
+      <c r="I63">
+        <v>2.79458279977587E-08</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tipo_Comunidade</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="D64">
+        <v>10</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0.7853981794336395</v>
+      </c>
+      <c r="G64">
+        <v>-1.776694117254477</v>
+      </c>
+      <c r="H64">
+        <v>1.776694117254477</v>
+      </c>
+      <c r="I64">
+        <v>4.177273346931159E-08</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tipo_Intervencao</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ethnobotanical survey</t>
+        </is>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>1.110720757145547</v>
+      </c>
+      <c r="G65">
+        <v>-3.083855209418343</v>
+      </c>
+      <c r="H65">
+        <v>3.083855209418343</v>
+      </c>
+      <c r="I65">
+        <v>2.869237346927056E-08</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Regiao</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="D66">
+        <v>11</v>
+      </c>
+      <c r="E66">
+        <v>0.3383752206437021</v>
+      </c>
+      <c r="F66">
+        <v>0.1346022800849774</v>
+      </c>
+      <c r="G66">
+        <v>0.03846265082042549</v>
+      </c>
+      <c r="H66">
+        <v>0.6382877904669786</v>
+      </c>
+      <c r="I66">
+        <v>2.03568301763085E-09</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Regiao</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>America Central</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>1.241823558557728</v>
+      </c>
+      <c r="G67">
+        <v>-3.952036795746309</v>
+      </c>
+      <c r="H67">
+        <v>3.952036795746309</v>
+      </c>
+      <c r="I67">
+        <v>3.819266496611709E-08</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Regiao</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>America do Sul</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>17</v>
+      </c>
+      <c r="E68">
+        <v>0.08884782282734541</v>
+      </c>
+      <c r="F68">
+        <v>0.4591668730198435</v>
+      </c>
+      <c r="G68">
+        <v>-0.884542464514274</v>
+      </c>
+      <c r="H68">
+        <v>1.062238110168965</v>
+      </c>
+      <c r="I68">
+        <v>2.477987656095375E-08</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Regiao</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>5</v>
+      </c>
+      <c r="E69">
+        <v>-0.1254234320546784</v>
+      </c>
+      <c r="F69">
+        <v>0.461170176151564</v>
+      </c>
+      <c r="G69">
+        <v>-1.405837110293893</v>
+      </c>
+      <c r="H69">
+        <v>1.154990246184536</v>
+      </c>
+      <c r="I69">
+        <v>1.879738385470305E-08</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Regiao</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>7</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0.9387303737320342</v>
+      </c>
+      <c r="G70">
+        <v>-2.296990476514661</v>
+      </c>
+      <c r="H70">
+        <v>2.296990476514661</v>
+      </c>
+      <c r="I70">
+        <v>3.192985951359382E-08</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Tipo_Comunidade</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Agricultores</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>14</v>
+      </c>
+      <c r="E71">
+        <v>0.3354217671074345</v>
+      </c>
+      <c r="F71">
+        <v>0.1317160184378479</v>
+      </c>
+      <c r="G71">
+        <v>0.05086660932023263</v>
+      </c>
+      <c r="H71">
+        <v>0.6199769248946365</v>
+      </c>
+      <c r="I71">
+        <v>3.405741867780223E-09</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tipo_Comunidade</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Indigena</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>18</v>
+      </c>
+      <c r="E72">
+        <v>0.07297666392599016</v>
+      </c>
+      <c r="F72">
+        <v>0.480850965720268</v>
+      </c>
+      <c r="G72">
+        <v>-0.9415301941668253</v>
+      </c>
+      <c r="H72">
+        <v>1.087483522018805</v>
+      </c>
+      <c r="I72">
+        <v>2.026781185966785E-08</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tipo_Comunidade</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>10</v>
+      </c>
+      <c r="E73">
+        <v>-0.1554443554844875</v>
+      </c>
+      <c r="F73">
+        <v>0.4560045989666084</v>
+      </c>
+      <c r="G73">
+        <v>-1.186998425305724</v>
+      </c>
+      <c r="H73">
+        <v>0.8761097143367487</v>
+      </c>
+      <c r="I73">
+        <v>3.076712788947562E-08</v>
       </c>
     </row>
   </sheetData>
